--- a/data/manual/wcag_validation_anonymised.xlsx
+++ b/data/manual/wcag_validation_anonymised.xlsx
@@ -1,27 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositorios\wcag-preconsent-tracking-university-websites\data\manual\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3D0718A-3A67-4B0A-AE87-2256A4421452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{14B09974-8B5D-46A9-8C44-A2EF7BB90AAB}"/>
   </bookViews>
   <sheets>
-    <sheet name="LEEME" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="validacion" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="doble_evaluacion" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="pares_kappa" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="README" sheetId="1" r:id="rId1"/>
+    <sheet name="validation" sheetId="2" r:id="rId2"/>
+    <sheet name="double evaluation" sheetId="3" r:id="rId3"/>
+    <sheet name="Kappa_pairs" sheetId="4" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">doble_evaluacion!$A$1:$R$16</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">pares_kappa!$A$1:$L$28</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">validacion!$A$1:$Q$46</definedName>
-  </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -30,43 +42,43 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="203">
   <si>
-    <t xml:space="preserve">Validacion manual de accesibilidad WCAG - conjunto de datos anonimizado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Submuestra de 15 sitios universitarios, tres criterios de exito, agosto de 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Criterios: 1.1.1 contenido no textual, 1.4.3 contraste minimo AA, 2.4.4 proposito del enlace en su contexto.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Codificacion: 1 = cumple (f=0)   P = parcial (f/n &lt;= 0,20)   0 = no cumple (f/n &gt; 0,20).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n = elementos inspeccionados; f = elementos que fallan el criterio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anonimizacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las personas evaluadoras aparecen como E01 a E10 (primera evaluacion) y D01 (segunda evaluacion).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los codigos se asignaron por orden de recepcion de las entregas y no codifican ningun atributo de las personas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Se han suprimido nombres, apellidos, nombres de archivo de entrega, horas de reloj y marcas horarias de las capturas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las horas de inicio y fin se sustituyen por la duracion en minutos, que conserva el valor metodologico sin identificar sesiones.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La correspondencia entre codigo y persona se conserva fuera de este deposito, bajo custodia del equipo investigador.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riesgo residual: dentro del grupo evaluador la combinacion de sitio asignado y fecha podria permitir reidentificacion. Quien reutilice estos datos no debe intentarlo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hojas</t>
+    <t>Validacion manual de accesibilidad WCAG - conjunto de datos anonimizado</t>
+  </si>
+  <si>
+    <t>Submuestra de 15 sitios universitarios, tres criterios de exito, agosto de 2026</t>
+  </si>
+  <si>
+    <t>Criterios: 1.1.1 contenido no textual, 1.4.3 contraste minimo AA, 2.4.4 proposito del enlace en su contexto.</t>
+  </si>
+  <si>
+    <t>Codificacion: 1 = cumple (f=0)   P = parcial (f/n &lt;= 0,20)   0 = no cumple (f/n &gt; 0,20).</t>
+  </si>
+  <si>
+    <t>n = elementos inspeccionados; f = elementos que fallan el criterio.</t>
+  </si>
+  <si>
+    <t>Anonimizacion</t>
+  </si>
+  <si>
+    <t>Las personas evaluadoras aparecen como E01 a E10 (primera evaluacion) y D01 (segunda evaluacion).</t>
+  </si>
+  <si>
+    <t>Los codigos se asignaron por orden de recepcion de las entregas y no codifican ningun atributo de las personas.</t>
+  </si>
+  <si>
+    <t>Se han suprimido nombres, apellidos, nombres de archivo de entrega, horas de reloj y marcas horarias de las capturas.</t>
+  </si>
+  <si>
+    <t>Las horas de inicio y fin se sustituyen por la duracion en minutos, que conserva el valor metodologico sin identificar sesiones.</t>
+  </si>
+  <si>
+    <t>La correspondencia entre codigo y persona se conserva fuera de este deposito, bajo custodia del equipo investigador.</t>
+  </si>
+  <si>
+    <t>Riesgo residual: dentro del grupo evaluador la combinacion de sitio asignado y fecha podria permitir reidentificacion. Quien reutilice estos datos no debe intentarlo.</t>
+  </si>
+  <si>
+    <t>Hojas</t>
   </si>
   <si>
     <t xml:space="preserve">  validacion         15 sitios x 3 criterios = 45 filas. Primera evaluacion, con la persona retenida por sitio tras la auditoria de las entregas.</t>
@@ -78,7 +90,7 @@
     <t xml:space="preserve">  pares_kappa        Los mismos 5 sitios, emparejando primera y segunda evaluacion, con el calculo de la kappa de Cohen.</t>
   </si>
   <si>
-    <t xml:space="preserve">Estado de cada sitio en la hoja validacion</t>
+    <t>Estado de cada sitio en la hoja validacion</t>
   </si>
   <si>
     <t xml:space="preserve">  ADMITIDA               codigo coherente con n/f, evidencia suficiente y sin conflicto pendiente.</t>
@@ -90,7 +102,7 @@
     <t xml:space="preserve">  NO ADMISIBLE           el n/f entregado no sostiene los codigos declarados. Se conservan por transparencia y no deben usarse en el analisis.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fiabilidad entre evaluadores</t>
+    <t>Fiabilidad entre evaluadores</t>
   </si>
   <si>
     <t xml:space="preserve">  14 pares, 10 coincidencias, po = 0,7143, pe = 0,4082, kappa de Cohen = 0,5172, kappa ponderada lineal = 0,4948.</t>
@@ -102,7 +114,7 @@
     <t xml:space="preserve">  Ninguno de los dos valores alcanza el umbral de 0,60, de modo que la doble codificacion sigue declarandose pendiente.</t>
   </si>
   <si>
-    <t xml:space="preserve">Limitaciones que deben citarse junto con estos datos</t>
+    <t>Limitaciones que deben citarse junto con estos datos</t>
   </si>
   <si>
     <t xml:space="preserve">  Cada persona construyo su propia muestra de elementos, de modo que los n no son comparables entre filas del mismo sitio.</t>
@@ -120,535 +132,540 @@
     <t xml:space="preserve">  Las capturas de pantalla originales no se depositan: contienen barras de tareas, perfiles de navegador y relojes de sistema que identifican a las personas.</t>
   </si>
   <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">grupo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sigla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">url</t>
-  </si>
-  <si>
-    <t xml:space="preserve">criterio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">criterio_nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">codigo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">f_sobre_n</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evaluador_cod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fecha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">duracion_min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">configuracion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">capturas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dictamen_tecnico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mundo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UC Berkeley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.berkeley.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contenido no textual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;100 % (declarado)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADMITIDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Informe PDF de 15 paginas con tabla n/f por criterio y una captura por criterio y sitio. Coincide con el dictamen previo del sitio (1.1.1=0 confirmado, 2.4.4=1 tras descartar enlaces identicos de igual proposito).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contraste minimo AA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proposito del enlace en su contexto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UCL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.ucl.ac.uk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coincide con el dictamen previo de UCL (1.1.1=1 aplicando la regla de redundancia H2; 1.4.3 f=0; 2.4.4=P).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cornell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.cornell.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifica el alt vacio de la seccion honeycomb y el CTA 'Keep reading' repetido con diez href distintos, verificado con el buscador de Elements.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://nus.edu.sg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADMITIDA CON RESERVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n=3 en 1.4.3 es el tamano muestral mas bajo del lote. Da por valida la tecnica title en img con alt vacio, lo que ACCNAME no respalda; ver evidencia de E06 para los iconos del pie.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Northwestern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.northwestern.edu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comprobado en vivo el 2026-09-01: 35 img en portada, ninguna sin alt ni con alt vacio. Respalda el codigo 1 frente a los codigos 0 de E02 y E03.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manchester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.manchester.ac.uk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unico evaluador de Manchester. Capturas con el recuadro de relacion de contraste de Chrome (5.57:1, AA 4.5 correcto) a 1280x720 y zoom 100 %.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HKUST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://hkust.edu.hk/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO ADMISIBLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Declara un unico n/f agregado (n=25 f=4) para los tres criterios, de modo que un mismo cociente 0,16 sustenta a la vez P y 0. Una captura muestra la consola con un script pegado que recorre y resalta enlaces, es decir la muestra de elementos se genero por script.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ecuador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNESUM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://unesum.edu.ec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1280x720, InPrivate, zoom 75 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unica evaluacion de UNESUM. Su propia captura de 1.4.3 muestra 3,46:1 con la marca 'AA: 3.0 correcto' y 'AAA: 4.5 no superado': es texto grande que cumple AA, asi que el unico fallo declarado no es fallo de 1.4.3 y el codigo correcto es 1. El recuento de 2.4.4 procede de un listado generado por script en la consola.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USECIPOL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://usecipol.edu.ec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidencia 1.1.1 solida: img de patron con alt='Patron decorativo' resaltada en Elements. El 1.4.3=1 repite el f=0 ya corregido a P en el dictamen previo de USECIPOL.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IAEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.iaen.edu.ec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comprobado en vivo el 2026-09-01: la portada declara aria-label 'ChatGPT Image 24 jun 2026, 10_44_26 a.m.' y 'Firefly_Gemini Flash...140699'. El 2.02:1 sobre rgb(110,193,228)=#6EC1E4 coincide con el dictamen previo de IAEN. Su 2.4.4=P subestima frente a f=19/26 de E04.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ULVR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.ulvr.edu.ec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comprobado en vivo: las 12 img de la portada llevan alt vacio, incluido logo_mini.png. Confirma f=1 y refuta el f=0 de E04. Panel de Accesibilidad con Name='' en la tarjeta GRADO.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UTPL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.utpl.edu.ec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1280x720; navegador con perfil y extensiones, no incognito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unica evaluacion de UTPL y la unica del lote con exactamente una captura por criterio, las tres correctas: img de costos.gif sin atributo alt; etiquetas 'LUGAR' y 'MODALIDAD' en #94a3b8 a 12 px con 2,56:1 y AA 4,5 no superado; boton flotante de WhatsApp cuyo unico contenido es un svg con aria-hidden. No declara observaciones descriptivas, solo n y f.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.ups.edu.ec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unico evaluador de UPS. Configuracion correcta y captura con tooltip de accesibilidad (Name vacio) sobre img alt vacio del slider. Aporta 1 de las 3 capturas exigidas por la seccion 6.1; la marca horaria de la captura (28/08 04:30) no concuerda con la fecha declarada.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UTI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.indoamerica.edu.ec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comprobado en vivo: 53 img, 46 con alt vacio y 2 sin atributo alt, lo que respalda el codigo 0 y refuta la P de E10. Su 2.4.4=1 queda en disputa frente a los enlaces sin nombre accesible documentados por E10.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECOTEC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://ecotec.edu.ec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mismo n/f agregado (n=25 f=1): incompatible con el codigo 1 de 1.4.3, que exige f=0. El informe docx no documenta el criterio 1.4.3 de ECOTEC.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">codigo_entregado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">codigo_admisible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n_declarado_unico_por_sitio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">f_declarado_unico_por_sitio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">coherente_con_nf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nodo_inspeccionado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">documenta_criterio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tipo_correccion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">justificacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">si</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img con alt="A scientist wearing a blue lab coat that reads 'university of california' on the left arm stands holding a pipette before machine.", loading=lazy, en el bloque 'Our research improves lives'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NINGUNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Una captura de un elemento que cumple no demuestra que f sea 0 en el resto de la muestra. El codigo se mantiene tal como se entrego, sin quedar confirmado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">body.home.wp-singular.page-template...; el panel de estilos muestra la lista de variables --wp--preset--color--*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sin ningun valor medido no hay nada que contradiga ni que confirme el codigo. Queda sin verificar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a.button.button--cta con href a news.berkeley.edu/2025/09/15/no-1-again-uc-berkeley-generates-more-startups-and-founders-than-any-other-university/ y texto 'Learn more', precedido del h2 'Creating more venture-backed startups than any other university in the world.'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4.4 admite que el proposito se determine por el contexto programatico del enlace. Lo mostrado es compatible con el codigo 1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a.link.link--overlay.link--large.link--accent con href a /students/support-and-wellbeing-services y texto 'How we support our students'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La captura no respalda el f=22 declarado, pero tampoco lo refuta. No hay correccion derivable de su propia evidencia.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a.link.link--large.link--accent con href a /about/our-people; estilos con color: var(--c-s-text-brand-inverse)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sin valor medido no hay correccion derivable. Queda sin verificar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">div.spotlight__content.col-12.col-lg-6; estilos con la paleta --ucl-*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sin ningun enlace inspeccionado no hay correccion derivable. Queda sin verificar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a.elementor-element...e-con.e-parent.e-lazyloaded con data-settings={"background_background":"classic"} y href a /la-unesum-fortalece-la-cooperacion-interinstitucional...; la imagen es fondo CSS, no un img</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARCIAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El patron mostrado no basta para declarar un fallo: la tarjeta tiene texto visible que puede operar como alternativa. No hay correccion derivable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">el mismo tipo de nodo a.elementor-element...; estilos con background-image: url(.../2026/08/UnesumQue...)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">h4.elementor-heading-title.elementor-size-default con el texto 'En linea'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">div.absolute.inset-0.rounded-2xl.ring-2.ring-transparent.transition-all.duration-500 con aria-hidden="true"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo mostrado no es un fallo de 1.1.1 sino la practica recomendada, pero tampoco refuta el f=8 declarado sobre otros elementos. No hay correccion derivable.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">div.relative.mx-auto.w-full.max-w-7xl.px-6.lg:px-8; estilos con reglas de padding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">el mismo div.absolute.inset-0...aria-hidden="true" de la captura de 1.1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">img.attachment-full.size-full.wp-image-16990.lazy.entered.loaded con alt vacio y src Captura-de-pantalla-2026-06-05-a-las-1.57.36-p.-m.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONFIRMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Al probar f mayor o igual que 1 su propia captura descarta el codigo 1. El codigo 0 que declaro es compatible con lo mostrado y con el recuento del sitio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">div.elementor-background-slideshow__slide.swiper-slide con aria-label="1 / 2" y opacity: 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXCLUIDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a.swiper-slide-inner con href a docs.google.com/forms/d/e/[ID]/viewform cuyo unico texto es el div.elementor-button 'Clic aqui'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORRIGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El codigo 1 exige f=0, de modo que su propia captura lo descarta. Para separar P de 0 hace falta un recuento del criterio, que no entrego; con el unico recuento que declaro para el sitio (n=15, f=7, cociente 0,467) el codigo resultante es 0.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evaluador_primera_cod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">codigo_primera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n_primera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">f_primera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evaluador_segunda_cod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">codigo_segunda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acuerdo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">entra_en_kappa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">motivo_exclusion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La captura de la segunda evaluacion muestra un enlace cuyo unico texto es 'Clic aqui', lo que descarta el codigo 1 declarado; el par se retira por evidencia contradictoria.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pares que entran en kappa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coincidencias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">po</t>
-  </si>
-  <si>
-    <t xml:space="preserve">codigos 0 - primera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">codigos P - primera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">codigos 1 - primera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">codigos 0 - segunda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">codigos P - segunda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">codigos 1 - segunda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kappa de Cohen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">umbral fijado para el manuscrito: 0,60</t>
+    <t>id</t>
+  </si>
+  <si>
+    <t>grupo</t>
+  </si>
+  <si>
+    <t>sigla</t>
+  </si>
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>criterio</t>
+  </si>
+  <si>
+    <t>criterio_nombre</t>
+  </si>
+  <si>
+    <t>codigo</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>f_sobre_n</t>
+  </si>
+  <si>
+    <t>evaluador_cod</t>
+  </si>
+  <si>
+    <t>fecha</t>
+  </si>
+  <si>
+    <t>duracion_min</t>
+  </si>
+  <si>
+    <t>configuracion</t>
+  </si>
+  <si>
+    <t>capturas</t>
+  </si>
+  <si>
+    <t>estado</t>
+  </si>
+  <si>
+    <t>dictamen_tecnico</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>mundo</t>
+  </si>
+  <si>
+    <t>UC Berkeley</t>
+  </si>
+  <si>
+    <t>https://www.berkeley.edu</t>
+  </si>
+  <si>
+    <t>1.1.1</t>
+  </si>
+  <si>
+    <t>contenido no textual</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>E01</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>&lt;100 % (declarado)</t>
+  </si>
+  <si>
+    <t>ADMITIDA</t>
+  </si>
+  <si>
+    <t>Informe PDF de 15 paginas con tabla n/f por criterio y una captura por criterio y sitio. Coincide con el dictamen previo del sitio (1.1.1=0 confirmado, 2.4.4=1 tras descartar enlaces identicos de igual proposito).</t>
+  </si>
+  <si>
+    <t>1.4.3</t>
+  </si>
+  <si>
+    <t>contraste minimo AA</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2.4.4</t>
+  </si>
+  <si>
+    <t>proposito del enlace en su contexto</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>UCL</t>
+  </si>
+  <si>
+    <t>https://www.ucl.ac.uk</t>
+  </si>
+  <si>
+    <t>Coincide con el dictamen previo de UCL (1.1.1=1 aplicando la regla de redundancia H2; 1.4.3 f=0; 2.4.4=P).</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Cornell</t>
+  </si>
+  <si>
+    <t>https://www.cornell.edu</t>
+  </si>
+  <si>
+    <t>Identifica el alt vacio de la seccion honeycomb y el CTA 'Keep reading' repetido con diez href distintos, verificado con el buscador de Elements.</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>NUS</t>
+  </si>
+  <si>
+    <t>https://nus.edu.sg</t>
+  </si>
+  <si>
+    <t>ADMITIDA CON RESERVA</t>
+  </si>
+  <si>
+    <t>n=3 en 1.4.3 es el tamano muestral mas bajo del lote. Da por valida la tecnica title en img con alt vacio, lo que ACCNAME no respalda; ver evidencia de E06 para los iconos del pie.</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Northwestern</t>
+  </si>
+  <si>
+    <t>https://www.northwestern.edu</t>
+  </si>
+  <si>
+    <t>Comprobado en vivo el 2026-09-01: 35 img en portada, ninguna sin alt ni con alt vacio. Respalda el codigo 1 frente a los codigos 0 de E02 y E03.</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>Manchester</t>
+  </si>
+  <si>
+    <t>https://www.manchester.ac.uk</t>
+  </si>
+  <si>
+    <t>E02</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>100 %</t>
+  </si>
+  <si>
+    <t>Unico evaluador de Manchester. Capturas con el recuadro de relacion de contraste de Chrome (5.57:1, AA 4.5 correcto) a 1280x720 y zoom 100 %.</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>HKUST</t>
+  </si>
+  <si>
+    <t>https://hkust.edu.hk/</t>
+  </si>
+  <si>
+    <t>E10</t>
+  </si>
+  <si>
+    <t>50 %</t>
+  </si>
+  <si>
+    <t>NO ADMISIBLE</t>
+  </si>
+  <si>
+    <t>Declara un unico n/f agregado (n=25 f=4) para los tres criterios, de modo que un mismo cociente 0,16 sustenta a la vez P y 0. Una captura muestra la consola con un script pegado que recorre y resalta enlaces, es decir la muestra de elementos se genero por script.</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>ecuador</t>
+  </si>
+  <si>
+    <t>UNESUM</t>
+  </si>
+  <si>
+    <t>https://unesum.edu.ec</t>
+  </si>
+  <si>
+    <t>E08</t>
+  </si>
+  <si>
+    <t>1280x720, InPrivate, zoom 75 %</t>
+  </si>
+  <si>
+    <t>Unica evaluacion de UNESUM. Su propia captura de 1.4.3 muestra 3,46:1 con la marca 'AA: 3.0 correcto' y 'AAA: 4.5 no superado': es texto grande que cumple AA, asi que el unico fallo declarado no es fallo de 1.4.3 y el codigo correcto es 1. El recuento de 2.4.4 procede de un listado generado por script en la consola.</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>USECIPOL</t>
+  </si>
+  <si>
+    <t>https://usecipol.edu.ec</t>
+  </si>
+  <si>
+    <t>Evidencia 1.1.1 solida: img de patron con alt='Patron decorativo' resaltada en Elements. El 1.4.3=1 repite el f=0 ya corregido a P en el dictamen previo de USECIPOL.</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>IAEN</t>
+  </si>
+  <si>
+    <t>https://www.iaen.edu.ec</t>
+  </si>
+  <si>
+    <t>E03</t>
+  </si>
+  <si>
+    <t>Comprobado en vivo el 2026-09-01: la portada declara aria-label 'ChatGPT Image 24 jun 2026, 10_44_26 a.m.' y 'Firefly_Gemini Flash...140699'. El 2.02:1 sobre rgb(110,193,228)=#6EC1E4 coincide con el dictamen previo de IAEN. Su 2.4.4=P subestima frente a f=19/26 de E04.</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>ULVR</t>
+  </si>
+  <si>
+    <t>https://www.ulvr.edu.ec</t>
+  </si>
+  <si>
+    <t>Comprobado en vivo: las 12 img de la portada llevan alt vacio, incluido logo_mini.png. Confirma f=1 y refuta el f=0 de E04. Panel de Accesibilidad con Name='' en la tarjeta GRADO.</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>UTPL</t>
+  </si>
+  <si>
+    <t>https://www.utpl.edu.ec</t>
+  </si>
+  <si>
+    <t>E09</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>1280x720; navegador con perfil y extensiones, no incognito</t>
+  </si>
+  <si>
+    <t>Unica evaluacion de UTPL y la unica del lote con exactamente una captura por criterio, las tres correctas: img de costos.gif sin atributo alt; etiquetas 'LUGAR' y 'MODALIDAD' en #94a3b8 a 12 px con 2,56:1 y AA 4,5 no superado; boton flotante de WhatsApp cuyo unico contenido es un svg con aria-hidden. No declara observaciones descriptivas, solo n y f.</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>UPS</t>
+  </si>
+  <si>
+    <t>https://www.ups.edu.ec</t>
+  </si>
+  <si>
+    <t>E05</t>
+  </si>
+  <si>
+    <t>Unico evaluador de UPS. Configuracion correcta y captura con tooltip de accesibilidad (Name vacio) sobre img alt vacio del slider. Aporta 1 de las 3 capturas exigidas por la seccion 6.1; la marca horaria de la captura (28/08 04:30) no concuerda con la fecha declarada.</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>UTI</t>
+  </si>
+  <si>
+    <t>https://www.indoamerica.edu.ec</t>
+  </si>
+  <si>
+    <t>Comprobado en vivo: 53 img, 46 con alt vacio y 2 sin atributo alt, lo que respalda el codigo 0 y refuta la P de E10. Su 2.4.4=1 queda en disputa frente a los enlaces sin nombre accesible documentados por E10.</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>ECOTEC</t>
+  </si>
+  <si>
+    <t>https://ecotec.edu.ec</t>
+  </si>
+  <si>
+    <t>Mismo n/f agregado (n=25 f=1): incompatible con el codigo 1 de 1.4.3, que exige f=0. El informe docx no documenta el criterio 1.4.3 de ECOTEC.</t>
+  </si>
+  <si>
+    <t>codigo_entregado</t>
+  </si>
+  <si>
+    <t>codigo_admisible</t>
+  </si>
+  <si>
+    <t>n_declarado_unico_por_sitio</t>
+  </si>
+  <si>
+    <t>f_declarado_unico_por_sitio</t>
+  </si>
+  <si>
+    <t>coherente_con_nf</t>
+  </si>
+  <si>
+    <t>nodo_inspeccionado</t>
+  </si>
+  <si>
+    <t>documenta_criterio</t>
+  </si>
+  <si>
+    <t>tipo_correccion</t>
+  </si>
+  <si>
+    <t>justificacion</t>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>D01</t>
+  </si>
+  <si>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>img con alt="A scientist wearing a blue lab coat that reads 'university of california' on the left arm stands holding a pipette before machine.", loading=lazy, en el bloque 'Our research improves lives'</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>NINGUNA</t>
+  </si>
+  <si>
+    <t>Una captura de un elemento que cumple no demuestra que f sea 0 en el resto de la muestra. El codigo se mantiene tal como se entrego, sin quedar confirmado.</t>
+  </si>
+  <si>
+    <t>body.home.wp-singular.page-template...; el panel de estilos muestra la lista de variables --wp--preset--color--*</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>Sin ningun valor medido no hay nada que contradiga ni que confirme el codigo. Queda sin verificar.</t>
+  </si>
+  <si>
+    <t>a.button.button--cta con href a news.berkeley.edu/2025/09/15/no-1-again-uc-berkeley-generates-more-startups-and-founders-than-any-other-university/ y texto 'Learn more', precedido del h2 'Creating more venture-backed startups than any other university in the world.'</t>
+  </si>
+  <si>
+    <t>2.4.4 admite que el proposito se determine por el contexto programatico del enlace. Lo mostrado es compatible con el codigo 1.</t>
+  </si>
+  <si>
+    <t>a.link.link--overlay.link--large.link--accent con href a /students/support-and-wellbeing-services y texto 'How we support our students'</t>
+  </si>
+  <si>
+    <t>La captura no respalda el f=22 declarado, pero tampoco lo refuta. No hay correccion derivable de su propia evidencia.</t>
+  </si>
+  <si>
+    <t>a.link.link--large.link--accent con href a /about/our-people; estilos con color: var(--c-s-text-brand-inverse)</t>
+  </si>
+  <si>
+    <t>Sin valor medido no hay correccion derivable. Queda sin verificar.</t>
+  </si>
+  <si>
+    <t>div.spotlight__content.col-12.col-lg-6; estilos con la paleta --ucl-*</t>
+  </si>
+  <si>
+    <t>Sin ningun enlace inspeccionado no hay correccion derivable. Queda sin verificar.</t>
+  </si>
+  <si>
+    <t>a.elementor-element...e-con.e-parent.e-lazyloaded con data-settings={"background_background":"classic"} y href a /la-unesum-fortalece-la-cooperacion-interinstitucional...; la imagen es fondo CSS, no un img</t>
+  </si>
+  <si>
+    <t>PARCIAL</t>
+  </si>
+  <si>
+    <t>El patron mostrado no basta para declarar un fallo: la tarjeta tiene texto visible que puede operar como alternativa. No hay correccion derivable.</t>
+  </si>
+  <si>
+    <t>el mismo tipo de nodo a.elementor-element...; estilos con background-image: url(.../2026/08/UnesumQue...)</t>
+  </si>
+  <si>
+    <t>h4.elementor-heading-title.elementor-size-default con el texto 'En linea'</t>
+  </si>
+  <si>
+    <t>div.absolute.inset-0.rounded-2xl.ring-2.ring-transparent.transition-all.duration-500 con aria-hidden="true"</t>
+  </si>
+  <si>
+    <t>Lo mostrado no es un fallo de 1.1.1 sino la practica recomendada, pero tampoco refuta el f=8 declarado sobre otros elementos. No hay correccion derivable.</t>
+  </si>
+  <si>
+    <t>div.relative.mx-auto.w-full.max-w-7xl.px-6.lg:px-8; estilos con reglas de padding</t>
+  </si>
+  <si>
+    <t>el mismo div.absolute.inset-0...aria-hidden="true" de la captura de 1.1.1</t>
+  </si>
+  <si>
+    <t>img.attachment-full.size-full.wp-image-16990.lazy.entered.loaded con alt vacio y src Captura-de-pantalla-2026-06-05-a-las-1.57.36-p.-m.png</t>
+  </si>
+  <si>
+    <t>CONFIRMA</t>
+  </si>
+  <si>
+    <t>Al probar f mayor o igual que 1 su propia captura descarta el codigo 1. El codigo 0 que declaro es compatible con lo mostrado y con el recuento del sitio.</t>
+  </si>
+  <si>
+    <t>div.elementor-background-slideshow__slide.swiper-slide con aria-label="1 / 2" y opacity: 0</t>
+  </si>
+  <si>
+    <t>EXCLUIDO</t>
+  </si>
+  <si>
+    <t>a.swiper-slide-inner con href a docs.google.com/forms/d/e/[ID]/viewform cuyo unico texto es el div.elementor-button 'Clic aqui'</t>
+  </si>
+  <si>
+    <t>CORRIGE</t>
+  </si>
+  <si>
+    <t>El codigo 1 exige f=0, de modo que su propia captura lo descarta. Para separar P de 0 hace falta un recuento del criterio, que no entrego; con el unico recuento que declaro para el sitio (n=15, f=7, cociente 0,467) el codigo resultante es 0.</t>
+  </si>
+  <si>
+    <t>evaluador_primera_cod</t>
+  </si>
+  <si>
+    <t>codigo_primera</t>
+  </si>
+  <si>
+    <t>n_primera</t>
+  </si>
+  <si>
+    <t>f_primera</t>
+  </si>
+  <si>
+    <t>evaluador_segunda_cod</t>
+  </si>
+  <si>
+    <t>codigo_segunda</t>
+  </si>
+  <si>
+    <t>acuerdo</t>
+  </si>
+  <si>
+    <t>entra_en_kappa</t>
+  </si>
+  <si>
+    <t>motivo_exclusion</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>La captura de la segunda evaluacion muestra un enlace cuyo unico texto es 'Clic aqui', lo que descarta el codigo 1 declarado; el par se retira por evidencia contradictoria.</t>
+  </si>
+  <si>
+    <t>Pares que entran en kappa</t>
+  </si>
+  <si>
+    <t>Coincidencias</t>
+  </si>
+  <si>
+    <t>po</t>
+  </si>
+  <si>
+    <t>codigos 0 - primera</t>
+  </si>
+  <si>
+    <t>codigos P - primera</t>
+  </si>
+  <si>
+    <t>codigos 1 - primera</t>
+  </si>
+  <si>
+    <t>codigos 0 - segunda</t>
+  </si>
+  <si>
+    <t>codigos P - segunda</t>
+  </si>
+  <si>
+    <t>codigos 1 - segunda</t>
+  </si>
+  <si>
+    <t>pe</t>
+  </si>
+  <si>
+    <t>kappa de Cohen</t>
+  </si>
+  <si>
+    <t>umbral fijado para el manuscrito: 0,60</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="11" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -657,85 +674,61 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="13"/>
       <color rgb="FF1F3864"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF1F3864"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFC00000"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -754,14 +747,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
@@ -777,384 +770,325 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="26">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="16">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{D92E14B0-CD2A-4CCA-A7EB-DA012D33199D}"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF1F3864"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF0000FF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC00000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFC00000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFC6EFCE"/>
-      <rgbColor rgb="FFFFEB9C"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFC7CE"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF1F3864"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -1165,4412 +1099,4306 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54702C67-F3DD-413B-975D-8052DD822728}">
   <dimension ref="A1:A36"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="120"/>
+    <col min="1" max="1" width="101.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3"/>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3"/>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3"/>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+    <row r="19" spans="1:1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+    <row r="23" spans="1:1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
+    <row r="24" spans="1:1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
+    <row r="32" spans="1:1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+    <row r="33" spans="1:1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
+    <row r="36" spans="1:1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
         <v>29</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D26303FA-47BF-4F7B-81F3-1F0B8612F876}">
   <dimension ref="A1:Q46"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="11" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="95"/>
+    <col min="17" max="17" width="54.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:17" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H2" s="9" t="n">
+      <c r="H2" s="10">
         <v>10</v>
       </c>
-      <c r="I2" s="9" t="n">
+      <c r="I2" s="10">
         <v>7</v>
       </c>
-      <c r="J2" s="9" t="n">
+      <c r="J2" s="10">
         <v>0.7</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M2" s="9" t="n">
+      <c r="M2" s="10">
         <v>54</v>
       </c>
-      <c r="N2" s="8" t="s">
+      <c r="N2" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="O2" s="9" t="n">
+      <c r="O2" s="10">
         <v>15</v>
       </c>
-      <c r="P2" s="10" t="s">
+      <c r="P2" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="Q2" s="8" t="s">
+      <c r="Q2" s="9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:17" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H3" s="9" t="n">
+      <c r="H3" s="10">
         <v>7</v>
       </c>
-      <c r="I3" s="9" t="n">
+      <c r="I3" s="10">
         <v>0</v>
       </c>
-      <c r="J3" s="9" t="n">
+      <c r="J3" s="10">
         <v>0</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M3" s="9" t="n">
+      <c r="M3" s="10">
         <v>54</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="O3" s="9" t="n">
+      <c r="O3" s="10">
         <v>15</v>
       </c>
-      <c r="P3" s="10" t="s">
+      <c r="P3" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="Q3" s="9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:17" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H4" s="9" t="n">
+      <c r="H4" s="10">
         <v>9</v>
       </c>
-      <c r="I4" s="9" t="n">
+      <c r="I4" s="10">
         <v>0</v>
       </c>
-      <c r="J4" s="9" t="n">
+      <c r="J4" s="10">
         <v>0</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M4" s="9" t="n">
+      <c r="M4" s="10">
         <v>54</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="N4" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="O4" s="9" t="n">
+      <c r="O4" s="10">
         <v>15</v>
       </c>
-      <c r="P4" s="10" t="s">
+      <c r="P4" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="Q4" s="8" t="s">
+      <c r="Q4" s="9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H5" s="9" t="n">
+      <c r="H5" s="10">
         <v>5</v>
       </c>
-      <c r="I5" s="9" t="n">
+      <c r="I5" s="10">
         <v>0</v>
       </c>
-      <c r="J5" s="9" t="n">
+      <c r="J5" s="10">
         <v>0</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M5" s="9" t="n">
+      <c r="M5" s="10">
         <v>35</v>
       </c>
-      <c r="N5" s="8" t="s">
+      <c r="N5" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="O5" s="9" t="n">
+      <c r="O5" s="10">
         <v>15</v>
       </c>
-      <c r="P5" s="10" t="s">
+      <c r="P5" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="Q5" s="8" t="s">
+      <c r="Q5" s="9" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H6" s="9" t="n">
+      <c r="H6" s="10">
         <v>4</v>
       </c>
-      <c r="I6" s="9" t="n">
+      <c r="I6" s="10">
         <v>0</v>
       </c>
-      <c r="J6" s="9" t="n">
+      <c r="J6" s="10">
         <v>0</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="M6" s="10">
         <v>35</v>
       </c>
-      <c r="N6" s="8" t="s">
+      <c r="N6" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="O6" s="9" t="n">
+      <c r="O6" s="10">
         <v>15</v>
       </c>
-      <c r="P6" s="10" t="s">
+      <c r="P6" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="Q6" s="8" t="s">
+      <c r="Q6" s="9" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H7" s="9" t="n">
+      <c r="H7" s="10">
         <v>16</v>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="I7" s="10">
         <v>2</v>
       </c>
-      <c r="J7" s="9" t="n">
+      <c r="J7" s="10">
         <v>0.125</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="9" t="n">
+      <c r="M7" s="10">
         <v>35</v>
       </c>
-      <c r="N7" s="8" t="s">
+      <c r="N7" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="O7" s="9" t="n">
+      <c r="O7" s="10">
         <v>15</v>
       </c>
-      <c r="P7" s="10" t="s">
+      <c r="P7" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="Q7" s="8" t="s">
+      <c r="Q7" s="9" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H8" s="9" t="n">
+      <c r="H8" s="10">
         <v>10</v>
       </c>
-      <c r="I8" s="9" t="n">
+      <c r="I8" s="10">
         <v>2</v>
       </c>
-      <c r="J8" s="9" t="n">
+      <c r="J8" s="10">
         <v>0.2</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M8" s="9" t="n">
+      <c r="M8" s="10">
         <v>32</v>
       </c>
-      <c r="N8" s="8" t="s">
+      <c r="N8" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="O8" s="9" t="n">
+      <c r="O8" s="10">
         <v>15</v>
       </c>
-      <c r="P8" s="10" t="s">
+      <c r="P8" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="Q8" s="8" t="s">
+      <c r="Q8" s="9" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="H9" s="10">
         <v>5</v>
       </c>
-      <c r="I9" s="9" t="n">
+      <c r="I9" s="10">
         <v>0</v>
       </c>
-      <c r="J9" s="9" t="n">
+      <c r="J9" s="10">
         <v>0</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="L9" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M9" s="9" t="n">
+      <c r="M9" s="10">
         <v>32</v>
       </c>
-      <c r="N9" s="8" t="s">
+      <c r="N9" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="O9" s="9" t="n">
+      <c r="O9" s="10">
         <v>15</v>
       </c>
-      <c r="P9" s="10" t="s">
+      <c r="P9" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="Q9" s="8" t="s">
+      <c r="Q9" s="9" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H10" s="9" t="n">
+      <c r="H10" s="10">
         <v>10</v>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="I10" s="10">
         <v>2</v>
       </c>
-      <c r="J10" s="9" t="n">
+      <c r="J10" s="10">
         <v>0.2</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M10" s="9" t="n">
+      <c r="M10" s="10">
         <v>32</v>
       </c>
-      <c r="N10" s="8" t="s">
+      <c r="N10" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="O10" s="9" t="n">
+      <c r="O10" s="10">
         <v>15</v>
       </c>
-      <c r="P10" s="10" t="s">
+      <c r="P10" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="Q10" s="8" t="s">
+      <c r="Q10" s="9" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H11" s="9" t="n">
+      <c r="H11" s="10">
         <v>11</v>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="I11" s="10">
         <v>1</v>
       </c>
-      <c r="J11" s="9" t="n">
-        <v>0.0909</v>
-      </c>
-      <c r="K11" s="6" t="s">
+      <c r="J11" s="10">
+        <v>9.0899999999999995E-2</v>
+      </c>
+      <c r="K11" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="L11" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M11" s="9" t="n">
+      <c r="M11" s="10">
         <v>51</v>
       </c>
-      <c r="N11" s="8" t="s">
+      <c r="N11" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="O11" s="9" t="n">
+      <c r="O11" s="10">
         <v>15</v>
       </c>
-      <c r="P11" s="10" t="s">
+      <c r="P11" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="Q11" s="8" t="s">
+      <c r="Q11" s="9" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H12" s="9" t="n">
+      <c r="H12" s="10">
         <v>3</v>
       </c>
-      <c r="I12" s="9" t="n">
+      <c r="I12" s="10">
         <v>1</v>
       </c>
-      <c r="J12" s="9" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="K12" s="6" t="s">
+      <c r="J12" s="10">
+        <v>0.33329999999999999</v>
+      </c>
+      <c r="K12" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="L12" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M12" s="9" t="n">
+      <c r="M12" s="10">
         <v>51</v>
       </c>
-      <c r="N12" s="8" t="s">
+      <c r="N12" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="O12" s="9" t="n">
+      <c r="O12" s="10">
         <v>15</v>
       </c>
-      <c r="P12" s="10" t="s">
+      <c r="P12" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="Q12" s="8" t="s">
+      <c r="Q12" s="9" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+    <row r="13" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H13" s="9" t="n">
+      <c r="H13" s="10">
         <v>11</v>
       </c>
-      <c r="I13" s="9" t="n">
+      <c r="I13" s="10">
         <v>3</v>
       </c>
-      <c r="J13" s="9" t="n">
+      <c r="J13" s="10">
         <v>0.2727</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="K13" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="L13" s="6" t="s">
+      <c r="L13" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M13" s="9" t="n">
+      <c r="M13" s="10">
         <v>51</v>
       </c>
-      <c r="N13" s="8" t="s">
+      <c r="N13" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="O13" s="9" t="n">
+      <c r="O13" s="10">
         <v>15</v>
       </c>
-      <c r="P13" s="10" t="s">
+      <c r="P13" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="Q13" s="8" t="s">
+      <c r="Q13" s="9" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H14" s="9" t="n">
+      <c r="H14" s="10">
         <v>11</v>
       </c>
-      <c r="I14" s="9" t="n">
+      <c r="I14" s="10">
         <v>0</v>
       </c>
-      <c r="J14" s="9" t="n">
+      <c r="J14" s="10">
         <v>0</v>
       </c>
-      <c r="K14" s="6" t="s">
+      <c r="K14" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="L14" s="6" t="s">
+      <c r="L14" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M14" s="9" t="n">
+      <c r="M14" s="10">
         <v>48</v>
       </c>
-      <c r="N14" s="8" t="s">
+      <c r="N14" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="O14" s="9" t="n">
+      <c r="O14" s="10">
         <v>15</v>
       </c>
-      <c r="P14" s="10" t="s">
+      <c r="P14" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="Q14" s="8" t="s">
+      <c r="Q14" s="9" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H15" s="9" t="n">
+      <c r="H15" s="10">
         <v>5</v>
       </c>
-      <c r="I15" s="9" t="n">
+      <c r="I15" s="10">
         <v>0</v>
       </c>
-      <c r="J15" s="9" t="n">
+      <c r="J15" s="10">
         <v>0</v>
       </c>
-      <c r="K15" s="6" t="s">
+      <c r="K15" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="L15" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M15" s="9" t="n">
+      <c r="M15" s="10">
         <v>48</v>
       </c>
-      <c r="N15" s="8" t="s">
+      <c r="N15" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="O15" s="9" t="n">
+      <c r="O15" s="10">
         <v>15</v>
       </c>
-      <c r="P15" s="10" t="s">
+      <c r="P15" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="Q15" s="8" t="s">
+      <c r="Q15" s="9" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+    <row r="16" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H16" s="9" t="n">
+      <c r="H16" s="10">
         <v>9</v>
       </c>
-      <c r="I16" s="9" t="n">
+      <c r="I16" s="10">
         <v>0</v>
       </c>
-      <c r="J16" s="9" t="n">
+      <c r="J16" s="10">
         <v>0</v>
       </c>
-      <c r="K16" s="6" t="s">
+      <c r="K16" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="L16" s="6" t="s">
+      <c r="L16" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M16" s="9" t="n">
+      <c r="M16" s="10">
         <v>48</v>
       </c>
-      <c r="N16" s="8" t="s">
+      <c r="N16" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="O16" s="9" t="n">
+      <c r="O16" s="10">
         <v>15</v>
       </c>
-      <c r="P16" s="10" t="s">
+      <c r="P16" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="Q16" s="8" t="s">
+      <c r="Q16" s="9" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+    <row r="17" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="9" t="n">
+      <c r="H17" s="10">
         <v>20</v>
       </c>
-      <c r="I17" s="9" t="n">
+      <c r="I17" s="10">
         <v>0</v>
       </c>
-      <c r="J17" s="9" t="n">
+      <c r="J17" s="10">
         <v>0</v>
       </c>
-      <c r="K17" s="6" t="s">
+      <c r="K17" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="L17" s="6" t="s">
+      <c r="L17" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="M17" s="9" t="n">
+      <c r="M17" s="10">
         <v>26</v>
       </c>
-      <c r="N17" s="8" t="s">
+      <c r="N17" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="O17" s="9" t="n">
+      <c r="O17" s="10">
         <v>11</v>
       </c>
-      <c r="P17" s="10" t="s">
+      <c r="P17" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="Q17" s="8" t="s">
+      <c r="Q17" s="9" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+    <row r="18" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H18" s="9" t="n">
+      <c r="H18" s="10">
         <v>25</v>
       </c>
-      <c r="I18" s="9" t="n">
+      <c r="I18" s="10">
         <v>2</v>
       </c>
-      <c r="J18" s="9" t="n">
+      <c r="J18" s="10">
         <v>0.08</v>
       </c>
-      <c r="K18" s="6" t="s">
+      <c r="K18" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="L18" s="6" t="s">
+      <c r="L18" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="M18" s="9" t="n">
+      <c r="M18" s="10">
         <v>26</v>
       </c>
-      <c r="N18" s="8" t="s">
+      <c r="N18" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="O18" s="9" t="n">
+      <c r="O18" s="10">
         <v>11</v>
       </c>
-      <c r="P18" s="10" t="s">
+      <c r="P18" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="Q18" s="8" t="s">
+      <c r="Q18" s="9" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+    <row r="19" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H19" s="9" t="n">
+      <c r="H19" s="10">
         <v>25</v>
       </c>
-      <c r="I19" s="9" t="n">
+      <c r="I19" s="10">
         <v>0</v>
       </c>
-      <c r="J19" s="9" t="n">
+      <c r="J19" s="10">
         <v>0</v>
       </c>
-      <c r="K19" s="6" t="s">
+      <c r="K19" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="L19" s="6" t="s">
+      <c r="L19" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="M19" s="9" t="n">
+      <c r="M19" s="10">
         <v>26</v>
       </c>
-      <c r="N19" s="8" t="s">
+      <c r="N19" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="O19" s="9" t="n">
+      <c r="O19" s="10">
         <v>11</v>
       </c>
-      <c r="P19" s="10" t="s">
+      <c r="P19" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="Q19" s="8" t="s">
+      <c r="Q19" s="9" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+    <row r="20" spans="1:17" ht="66" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H20" s="9" t="n">
+      <c r="H20" s="10">
         <v>25</v>
       </c>
-      <c r="I20" s="9" t="n">
+      <c r="I20" s="10">
         <v>4</v>
       </c>
-      <c r="J20" s="9" t="n">
+      <c r="J20" s="10">
         <v>0.16</v>
       </c>
-      <c r="K20" s="6" t="s">
+      <c r="K20" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="L20" s="6" t="s">
+      <c r="L20" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M20" s="9" t="n">
+      <c r="M20" s="10">
         <v>21</v>
       </c>
-      <c r="N20" s="8" t="s">
+      <c r="N20" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="O20" s="9" t="n">
+      <c r="O20" s="10">
         <v>8</v>
       </c>
-      <c r="P20" s="10" t="s">
+      <c r="P20" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="Q20" s="8" t="s">
+      <c r="Q20" s="9" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
+    <row r="21" spans="1:17" ht="66" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H21" s="9" t="n">
+      <c r="H21" s="10">
         <v>25</v>
       </c>
-      <c r="I21" s="9" t="n">
+      <c r="I21" s="10">
         <v>4</v>
       </c>
-      <c r="J21" s="9" t="n">
+      <c r="J21" s="10">
         <v>0.16</v>
       </c>
-      <c r="K21" s="6" t="s">
+      <c r="K21" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="L21" s="6" t="s">
+      <c r="L21" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M21" s="9" t="n">
+      <c r="M21" s="10">
         <v>21</v>
       </c>
-      <c r="N21" s="8" t="s">
+      <c r="N21" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="O21" s="9" t="n">
+      <c r="O21" s="10">
         <v>8</v>
       </c>
-      <c r="P21" s="10" t="s">
+      <c r="P21" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="Q21" s="8" t="s">
+      <c r="Q21" s="9" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+    <row r="22" spans="1:17" ht="66" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H22" s="9" t="n">
+      <c r="H22" s="10">
         <v>25</v>
       </c>
-      <c r="I22" s="9" t="n">
+      <c r="I22" s="10">
         <v>4</v>
       </c>
-      <c r="J22" s="9" t="n">
+      <c r="J22" s="10">
         <v>0.16</v>
       </c>
-      <c r="K22" s="6" t="s">
+      <c r="K22" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="L22" s="6" t="s">
+      <c r="L22" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M22" s="9" t="n">
+      <c r="M22" s="10">
         <v>21</v>
       </c>
-      <c r="N22" s="8" t="s">
+      <c r="N22" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="O22" s="9" t="n">
+      <c r="O22" s="10">
         <v>8</v>
       </c>
-      <c r="P22" s="10" t="s">
+      <c r="P22" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="Q22" s="8" t="s">
+      <c r="Q22" s="9" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+    <row r="23" spans="1:17" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H23" s="9" t="n">
+      <c r="H23" s="10">
         <v>27</v>
       </c>
-      <c r="I23" s="9" t="n">
+      <c r="I23" s="10">
         <v>6</v>
       </c>
-      <c r="J23" s="9" t="n">
-        <v>0.2222</v>
-      </c>
-      <c r="K23" s="6" t="s">
+      <c r="J23" s="10">
+        <v>0.22220000000000001</v>
+      </c>
+      <c r="K23" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="L23" s="6" t="s">
+      <c r="L23" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="M23" s="9" t="n">
+      <c r="M23" s="10">
         <v>42</v>
       </c>
-      <c r="N23" s="8" t="s">
+      <c r="N23" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="O23" s="9" t="n">
+      <c r="O23" s="10">
         <v>11</v>
       </c>
-      <c r="P23" s="10" t="s">
+      <c r="P23" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="Q23" s="8" t="s">
+      <c r="Q23" s="9" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+    <row r="24" spans="1:17" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H24" s="9" t="n">
+      <c r="H24" s="10">
         <v>18</v>
       </c>
-      <c r="I24" s="9" t="n">
+      <c r="I24" s="10">
         <v>1</v>
       </c>
-      <c r="J24" s="9" t="n">
-        <v>0.0556</v>
-      </c>
-      <c r="K24" s="6" t="s">
+      <c r="J24" s="10">
+        <v>5.5599999999999997E-2</v>
+      </c>
+      <c r="K24" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="L24" s="6" t="s">
+      <c r="L24" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="M24" s="9" t="n">
+      <c r="M24" s="10">
         <v>42</v>
       </c>
-      <c r="N24" s="8" t="s">
+      <c r="N24" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="O24" s="9" t="n">
+      <c r="O24" s="10">
         <v>11</v>
       </c>
-      <c r="P24" s="10" t="s">
+      <c r="P24" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="Q24" s="8" t="s">
+      <c r="Q24" s="9" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
+    <row r="25" spans="1:17" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="8" t="s">
+      <c r="D25" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H25" s="9" t="n">
+      <c r="H25" s="10">
         <v>25</v>
       </c>
-      <c r="I25" s="9" t="n">
+      <c r="I25" s="10">
         <v>8</v>
       </c>
-      <c r="J25" s="9" t="n">
+      <c r="J25" s="10">
         <v>0.32</v>
       </c>
-      <c r="K25" s="6" t="s">
+      <c r="K25" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="L25" s="6" t="s">
+      <c r="L25" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="M25" s="9" t="n">
+      <c r="M25" s="10">
         <v>42</v>
       </c>
-      <c r="N25" s="8" t="s">
+      <c r="N25" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="O25" s="9" t="n">
+      <c r="O25" s="10">
         <v>11</v>
       </c>
-      <c r="P25" s="10" t="s">
+      <c r="P25" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="Q25" s="8" t="s">
+      <c r="Q25" s="9" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+    <row r="26" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="D26" s="8" t="s">
+      <c r="D26" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H26" s="9" t="n">
+      <c r="H26" s="10">
         <v>17</v>
       </c>
-      <c r="I26" s="9" t="n">
+      <c r="I26" s="10">
         <v>7</v>
       </c>
-      <c r="J26" s="9" t="n">
+      <c r="J26" s="10">
         <v>0.4118</v>
       </c>
-      <c r="K26" s="6" t="s">
+      <c r="K26" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="L26" s="6" t="s">
+      <c r="L26" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="M26" s="9" t="n">
+      <c r="M26" s="10">
         <v>25</v>
       </c>
-      <c r="N26" s="8" t="s">
+      <c r="N26" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="O26" s="9" t="n">
+      <c r="O26" s="10">
         <v>11</v>
       </c>
-      <c r="P26" s="10" t="s">
+      <c r="P26" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="Q26" s="8" t="s">
+      <c r="Q26" s="9" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+    <row r="27" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H27" s="9" t="n">
+      <c r="H27" s="10">
         <v>25</v>
       </c>
-      <c r="I27" s="9" t="n">
+      <c r="I27" s="10">
         <v>0</v>
       </c>
-      <c r="J27" s="9" t="n">
+      <c r="J27" s="10">
         <v>0</v>
       </c>
-      <c r="K27" s="6" t="s">
+      <c r="K27" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="L27" s="6" t="s">
+      <c r="L27" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="M27" s="9" t="n">
+      <c r="M27" s="10">
         <v>25</v>
       </c>
-      <c r="N27" s="8" t="s">
+      <c r="N27" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="O27" s="9" t="n">
+      <c r="O27" s="10">
         <v>11</v>
       </c>
-      <c r="P27" s="10" t="s">
+      <c r="P27" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="Q27" s="8" t="s">
+      <c r="Q27" s="9" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
+    <row r="28" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="E28" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H28" s="9" t="n">
+      <c r="H28" s="10">
         <v>25</v>
       </c>
-      <c r="I28" s="9" t="n">
+      <c r="I28" s="10">
         <v>0</v>
       </c>
-      <c r="J28" s="9" t="n">
+      <c r="J28" s="10">
         <v>0</v>
       </c>
-      <c r="K28" s="6" t="s">
+      <c r="K28" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="L28" s="6" t="s">
+      <c r="L28" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="M28" s="9" t="n">
+      <c r="M28" s="10">
         <v>25</v>
       </c>
-      <c r="N28" s="8" t="s">
+      <c r="N28" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="O28" s="9" t="n">
+      <c r="O28" s="10">
         <v>11</v>
       </c>
-      <c r="P28" s="10" t="s">
+      <c r="P28" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="Q28" s="8" t="s">
+      <c r="Q28" s="9" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+    <row r="29" spans="1:17" ht="66" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="D29" s="8" t="s">
+      <c r="D29" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H29" s="9" t="n">
+      <c r="H29" s="10">
         <v>7</v>
       </c>
-      <c r="I29" s="9" t="n">
+      <c r="I29" s="10">
         <v>2</v>
       </c>
-      <c r="J29" s="9" t="n">
-        <v>0.2857</v>
-      </c>
-      <c r="K29" s="6" t="s">
+      <c r="J29" s="10">
+        <v>0.28570000000000001</v>
+      </c>
+      <c r="K29" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="L29" s="6" t="s">
+      <c r="L29" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="M29" s="9" t="n">
+      <c r="M29" s="10">
         <v>65</v>
       </c>
-      <c r="N29" s="8" t="s">
+      <c r="N29" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="O29" s="9" t="n">
+      <c r="O29" s="10">
         <v>7</v>
       </c>
-      <c r="P29" s="10" t="s">
+      <c r="P29" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="Q29" s="8" t="s">
+      <c r="Q29" s="9" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
+    <row r="30" spans="1:17" ht="66" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="D30" s="8" t="s">
+      <c r="D30" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G30" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H30" s="9" t="n">
+      <c r="H30" s="10">
         <v>16</v>
       </c>
-      <c r="I30" s="9" t="n">
+      <c r="I30" s="10">
         <v>4</v>
       </c>
-      <c r="J30" s="9" t="n">
+      <c r="J30" s="10">
         <v>0.25</v>
       </c>
-      <c r="K30" s="6" t="s">
+      <c r="K30" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="L30" s="6" t="s">
+      <c r="L30" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="M30" s="9" t="n">
+      <c r="M30" s="10">
         <v>65</v>
       </c>
-      <c r="N30" s="8" t="s">
+      <c r="N30" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="O30" s="9" t="n">
+      <c r="O30" s="10">
         <v>7</v>
       </c>
-      <c r="P30" s="10" t="s">
+      <c r="P30" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="Q30" s="8" t="s">
+      <c r="Q30" s="9" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
+    <row r="31" spans="1:17" ht="66" x14ac:dyDescent="0.3">
+      <c r="A31" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="G31" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H31" s="9" t="n">
+      <c r="H31" s="10">
         <v>18</v>
       </c>
-      <c r="I31" s="9" t="n">
+      <c r="I31" s="10">
         <v>2</v>
       </c>
-      <c r="J31" s="9" t="n">
+      <c r="J31" s="10">
         <v>0.1111</v>
       </c>
-      <c r="K31" s="6" t="s">
+      <c r="K31" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="L31" s="6" t="s">
+      <c r="L31" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="M31" s="9" t="n">
+      <c r="M31" s="10">
         <v>65</v>
       </c>
-      <c r="N31" s="8" t="s">
+      <c r="N31" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="O31" s="9" t="n">
+      <c r="O31" s="10">
         <v>7</v>
       </c>
-      <c r="P31" s="10" t="s">
+      <c r="P31" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="Q31" s="8" t="s">
+      <c r="Q31" s="9" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+    <row r="32" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="G32" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H32" s="9" t="n">
+      <c r="H32" s="10">
         <v>8</v>
       </c>
-      <c r="I32" s="9" t="n">
+      <c r="I32" s="10">
         <v>1</v>
       </c>
-      <c r="J32" s="9" t="n">
+      <c r="J32" s="10">
         <v>0.125</v>
       </c>
-      <c r="K32" s="6" t="s">
+      <c r="K32" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="L32" s="6" t="s">
+      <c r="L32" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="M32" s="9" t="n">
+      <c r="M32" s="10">
         <v>75</v>
       </c>
-      <c r="N32" s="8" t="s">
+      <c r="N32" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="O32" s="9" t="n">
+      <c r="O32" s="10">
         <v>7</v>
       </c>
-      <c r="P32" s="10" t="s">
+      <c r="P32" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="Q32" s="8" t="s">
+      <c r="Q32" s="9" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+    <row r="33" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="G33" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H33" s="9" t="n">
+      <c r="H33" s="10">
         <v>15</v>
       </c>
-      <c r="I33" s="9" t="n">
+      <c r="I33" s="10">
         <v>6</v>
       </c>
-      <c r="J33" s="9" t="n">
+      <c r="J33" s="10">
         <v>0.4</v>
       </c>
-      <c r="K33" s="6" t="s">
+      <c r="K33" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="L33" s="6" t="s">
+      <c r="L33" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="M33" s="9" t="n">
+      <c r="M33" s="10">
         <v>75</v>
       </c>
-      <c r="N33" s="8" t="s">
+      <c r="N33" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="O33" s="9" t="n">
+      <c r="O33" s="10">
         <v>7</v>
       </c>
-      <c r="P33" s="10" t="s">
+      <c r="P33" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="Q33" s="8" t="s">
+      <c r="Q33" s="9" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
+    <row r="34" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="G34" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H34" s="9" t="n">
+      <c r="H34" s="10">
         <v>25</v>
       </c>
-      <c r="I34" s="9" t="n">
+      <c r="I34" s="10">
         <v>10</v>
       </c>
-      <c r="J34" s="9" t="n">
+      <c r="J34" s="10">
         <v>0.4</v>
       </c>
-      <c r="K34" s="6" t="s">
+      <c r="K34" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="L34" s="6" t="s">
+      <c r="L34" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="M34" s="9" t="n">
+      <c r="M34" s="10">
         <v>75</v>
       </c>
-      <c r="N34" s="8" t="s">
+      <c r="N34" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="O34" s="9" t="n">
+      <c r="O34" s="10">
         <v>7</v>
       </c>
-      <c r="P34" s="10" t="s">
+      <c r="P34" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="Q34" s="8" t="s">
+      <c r="Q34" s="9" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
+    <row r="35" spans="1:17" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="G35" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H35" s="9" t="n">
+      <c r="H35" s="10">
         <v>24</v>
       </c>
-      <c r="I35" s="9" t="n">
+      <c r="I35" s="10">
         <v>5</v>
       </c>
-      <c r="J35" s="9" t="n">
-        <v>0.2083</v>
-      </c>
-      <c r="K35" s="6" t="s">
+      <c r="J35" s="10">
+        <v>0.20830000000000001</v>
+      </c>
+      <c r="K35" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="L35" s="6" t="s">
+      <c r="L35" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="M35" s="9" t="n">
+      <c r="M35" s="10">
         <v>45</v>
       </c>
-      <c r="N35" s="8" t="s">
+      <c r="N35" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="O35" s="9" t="n">
+      <c r="O35" s="10">
         <v>3</v>
       </c>
-      <c r="P35" s="10" t="s">
+      <c r="P35" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="Q35" s="8" t="s">
+      <c r="Q35" s="9" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
+    <row r="36" spans="1:17" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E36" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G36" s="6" t="s">
+      <c r="G36" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H36" s="9" t="n">
+      <c r="H36" s="10">
         <v>15</v>
       </c>
-      <c r="I36" s="9" t="n">
+      <c r="I36" s="10">
         <v>2</v>
       </c>
-      <c r="J36" s="9" t="n">
+      <c r="J36" s="10">
         <v>0.1333</v>
       </c>
-      <c r="K36" s="6" t="s">
+      <c r="K36" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="L36" s="6" t="s">
+      <c r="L36" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="M36" s="9" t="n">
+      <c r="M36" s="10">
         <v>45</v>
       </c>
-      <c r="N36" s="8" t="s">
+      <c r="N36" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="O36" s="9" t="n">
+      <c r="O36" s="10">
         <v>3</v>
       </c>
-      <c r="P36" s="10" t="s">
+      <c r="P36" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="Q36" s="8" t="s">
+      <c r="Q36" s="9" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
+    <row r="37" spans="1:17" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D37" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E37" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G37" s="6" t="s">
+      <c r="G37" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H37" s="9" t="n">
+      <c r="H37" s="10">
         <v>25</v>
       </c>
-      <c r="I37" s="9" t="n">
+      <c r="I37" s="10">
         <v>2</v>
       </c>
-      <c r="J37" s="9" t="n">
+      <c r="J37" s="10">
         <v>0.08</v>
       </c>
-      <c r="K37" s="6" t="s">
+      <c r="K37" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="L37" s="6" t="s">
+      <c r="L37" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="M37" s="9" t="n">
+      <c r="M37" s="10">
         <v>45</v>
       </c>
-      <c r="N37" s="8" t="s">
+      <c r="N37" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="O37" s="9" t="n">
+      <c r="O37" s="10">
         <v>3</v>
       </c>
-      <c r="P37" s="10" t="s">
+      <c r="P37" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="Q37" s="8" t="s">
+      <c r="Q37" s="9" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="s">
+    <row r="38" spans="1:17" ht="66" x14ac:dyDescent="0.3">
+      <c r="A38" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="D38" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="E38" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="7" t="s">
+      <c r="F38" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G38" s="6" t="s">
+      <c r="G38" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H38" s="9" t="n">
+      <c r="H38" s="10">
         <v>25</v>
       </c>
-      <c r="I38" s="9" t="n">
+      <c r="I38" s="10">
         <v>7</v>
       </c>
-      <c r="J38" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="K38" s="6" t="s">
+      <c r="J38" s="10">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="K38" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="L38" s="6" t="s">
+      <c r="L38" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="M38" s="9" t="n">
+      <c r="M38" s="10">
         <v>14</v>
       </c>
-      <c r="N38" s="8" t="s">
+      <c r="N38" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="O38" s="9" t="n">
+      <c r="O38" s="10">
         <v>4</v>
       </c>
-      <c r="P38" s="10" t="s">
+      <c r="P38" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="Q38" s="8" t="s">
+      <c r="Q38" s="9" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6" t="s">
+    <row r="39" spans="1:17" ht="66" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D39" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F39" s="7" t="s">
+      <c r="F39" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G39" s="6" t="s">
+      <c r="G39" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H39" s="9" t="n">
+      <c r="H39" s="10">
         <v>25</v>
       </c>
-      <c r="I39" s="9" t="n">
+      <c r="I39" s="10">
         <v>4</v>
       </c>
-      <c r="J39" s="9" t="n">
+      <c r="J39" s="10">
         <v>0.16</v>
       </c>
-      <c r="K39" s="6" t="s">
+      <c r="K39" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="L39" s="6" t="s">
+      <c r="L39" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="M39" s="9" t="n">
+      <c r="M39" s="10">
         <v>14</v>
       </c>
-      <c r="N39" s="8" t="s">
+      <c r="N39" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="O39" s="9" t="n">
+      <c r="O39" s="10">
         <v>4</v>
       </c>
-      <c r="P39" s="10" t="s">
+      <c r="P39" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="Q39" s="8" t="s">
+      <c r="Q39" s="9" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="s">
+    <row r="40" spans="1:17" ht="66" x14ac:dyDescent="0.3">
+      <c r="A40" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D40" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E40" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F40" s="7" t="s">
+      <c r="F40" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G40" s="6" t="s">
+      <c r="G40" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H40" s="9" t="n">
+      <c r="H40" s="10">
         <v>25</v>
       </c>
-      <c r="I40" s="9" t="n">
+      <c r="I40" s="10">
         <v>3</v>
       </c>
-      <c r="J40" s="9" t="n">
+      <c r="J40" s="10">
         <v>0.12</v>
       </c>
-      <c r="K40" s="6" t="s">
+      <c r="K40" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="L40" s="6" t="s">
+      <c r="L40" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="M40" s="9" t="n">
+      <c r="M40" s="10">
         <v>14</v>
       </c>
-      <c r="N40" s="8" t="s">
+      <c r="N40" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="O40" s="9" t="n">
+      <c r="O40" s="10">
         <v>4</v>
       </c>
-      <c r="P40" s="10" t="s">
+      <c r="P40" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="Q40" s="8" t="s">
+      <c r="Q40" s="9" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6" t="s">
+    <row r="41" spans="1:17" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="D41" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F41" s="7" t="s">
+      <c r="F41" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G41" s="6" t="s">
+      <c r="G41" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H41" s="9" t="n">
+      <c r="H41" s="10">
         <v>25</v>
       </c>
-      <c r="I41" s="9" t="n">
+      <c r="I41" s="10">
         <v>6</v>
       </c>
-      <c r="J41" s="9" t="n">
+      <c r="J41" s="10">
         <v>0.24</v>
       </c>
-      <c r="K41" s="6" t="s">
+      <c r="K41" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="L41" s="6" t="s">
+      <c r="L41" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="M41" s="9" t="n">
+      <c r="M41" s="10">
         <v>10</v>
       </c>
-      <c r="N41" s="8" t="s">
+      <c r="N41" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="O41" s="9" t="n">
+      <c r="O41" s="10">
         <v>4</v>
       </c>
-      <c r="P41" s="10" t="s">
+      <c r="P41" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="Q41" s="8" t="s">
+      <c r="Q41" s="9" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="s">
+    <row r="42" spans="1:17" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="D42" s="8" t="s">
+      <c r="D42" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E42" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F42" s="7" t="s">
+      <c r="F42" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G42" s="6" t="s">
+      <c r="G42" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H42" s="9" t="n">
+      <c r="H42" s="10">
         <v>25</v>
       </c>
-      <c r="I42" s="9" t="n">
+      <c r="I42" s="10">
         <v>4</v>
       </c>
-      <c r="J42" s="9" t="n">
+      <c r="J42" s="10">
         <v>0.16</v>
       </c>
-      <c r="K42" s="6" t="s">
+      <c r="K42" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="L42" s="6" t="s">
+      <c r="L42" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="M42" s="9" t="n">
+      <c r="M42" s="10">
         <v>10</v>
       </c>
-      <c r="N42" s="8" t="s">
+      <c r="N42" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="O42" s="9" t="n">
+      <c r="O42" s="10">
         <v>4</v>
       </c>
-      <c r="P42" s="10" t="s">
+      <c r="P42" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="Q42" s="8" t="s">
+      <c r="Q42" s="9" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="s">
+    <row r="43" spans="1:17" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D43" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="E43" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F43" s="7" t="s">
+      <c r="F43" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G43" s="6" t="s">
+      <c r="G43" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H43" s="9" t="n">
+      <c r="H43" s="10">
         <v>25</v>
       </c>
-      <c r="I43" s="9" t="n">
+      <c r="I43" s="10">
         <v>0</v>
       </c>
-      <c r="J43" s="9" t="n">
+      <c r="J43" s="10">
         <v>0</v>
       </c>
-      <c r="K43" s="6" t="s">
+      <c r="K43" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="L43" s="6" t="s">
+      <c r="L43" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="M43" s="9" t="n">
+      <c r="M43" s="10">
         <v>10</v>
       </c>
-      <c r="N43" s="8" t="s">
+      <c r="N43" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="O43" s="9" t="n">
+      <c r="O43" s="10">
         <v>4</v>
       </c>
-      <c r="P43" s="10" t="s">
+      <c r="P43" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="Q43" s="8" t="s">
+      <c r="Q43" s="9" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="s">
+    <row r="44" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="D44" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="E44" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F44" s="7" t="s">
+      <c r="F44" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="G44" s="6" t="s">
+      <c r="G44" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H44" s="9" t="n">
+      <c r="H44" s="10">
         <v>25</v>
       </c>
-      <c r="I44" s="9" t="n">
+      <c r="I44" s="10">
         <v>1</v>
       </c>
-      <c r="J44" s="9" t="n">
+      <c r="J44" s="10">
         <v>0.04</v>
       </c>
-      <c r="K44" s="6" t="s">
+      <c r="K44" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="L44" s="6" t="s">
+      <c r="L44" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M44" s="9" t="n">
+      <c r="M44" s="10">
         <v>22</v>
       </c>
-      <c r="N44" s="8" t="s">
+      <c r="N44" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="O44" s="9" t="n">
+      <c r="O44" s="10">
         <v>8</v>
       </c>
-      <c r="P44" s="10" t="s">
+      <c r="P44" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="Q44" s="8" t="s">
+      <c r="Q44" s="9" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6" t="s">
+    <row r="45" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="D45" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="E45" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F45" s="7" t="s">
+      <c r="F45" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G45" s="6" t="s">
+      <c r="G45" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H45" s="9" t="n">
+      <c r="H45" s="10">
         <v>25</v>
       </c>
-      <c r="I45" s="9" t="n">
+      <c r="I45" s="10">
         <v>1</v>
       </c>
-      <c r="J45" s="9" t="n">
+      <c r="J45" s="10">
         <v>0.04</v>
       </c>
-      <c r="K45" s="6" t="s">
+      <c r="K45" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="L45" s="6" t="s">
+      <c r="L45" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M45" s="9" t="n">
+      <c r="M45" s="10">
         <v>22</v>
       </c>
-      <c r="N45" s="8" t="s">
+      <c r="N45" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="O45" s="9" t="n">
+      <c r="O45" s="10">
         <v>8</v>
       </c>
-      <c r="P45" s="10" t="s">
+      <c r="P45" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="Q45" s="8" t="s">
+      <c r="Q45" s="9" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6" t="s">
+    <row r="46" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D46" s="8" t="s">
+      <c r="D46" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F46" s="7" t="s">
+      <c r="F46" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="G46" s="6" t="s">
+      <c r="G46" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H46" s="9" t="n">
+      <c r="H46" s="10">
         <v>25</v>
       </c>
-      <c r="I46" s="9" t="n">
+      <c r="I46" s="10">
         <v>1</v>
       </c>
-      <c r="J46" s="9" t="n">
+      <c r="J46" s="10">
         <v>0.04</v>
       </c>
-      <c r="K46" s="6" t="s">
+      <c r="K46" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="L46" s="6" t="s">
+      <c r="L46" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M46" s="9" t="n">
+      <c r="M46" s="10">
         <v>22</v>
       </c>
-      <c r="N46" s="8" t="s">
+      <c r="N46" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="O46" s="9" t="n">
+      <c r="O46" s="10">
         <v>8</v>
       </c>
-      <c r="P46" s="10" t="s">
+      <c r="P46" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="Q46" s="8" t="s">
+      <c r="Q46" s="9" t="s">
         <v>135</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q46"/>
-  <conditionalFormatting sqref="P2:P46">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
-      <formula>"ADMITIDA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
-      <formula>"ADMITIDA CON RESERVA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
-      <formula>"NO ADMISIBLE"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2534942-6AA0-465E-B722-2E4FE47C8E4C}">
   <dimension ref="A1:R16"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="12" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="80"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="90"/>
+    <col min="15" max="15" width="57.33203125" customWidth="1"/>
+    <col min="18" max="18" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:18" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="12" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:18" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="I2" s="9" t="n">
+      <c r="I2" s="16">
         <v>17</v>
       </c>
-      <c r="J2" s="9" t="n">
+      <c r="J2" s="16">
         <v>0</v>
       </c>
-      <c r="K2" s="9" t="n">
+      <c r="K2" s="16">
         <v>0</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="O2" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="Q2" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="R2" s="8" t="s">
+      <c r="R2" s="15" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:18" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="I3" s="9" t="n">
+      <c r="I3" s="16">
         <v>17</v>
       </c>
-      <c r="J3" s="9" t="n">
+      <c r="J3" s="16">
         <v>0</v>
       </c>
-      <c r="K3" s="9" t="n">
+      <c r="K3" s="16">
         <v>0</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="R3" s="8" t="s">
+      <c r="R3" s="15" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:18" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="9" t="n">
+      <c r="I4" s="16">
         <v>17</v>
       </c>
-      <c r="J4" s="9" t="n">
+      <c r="J4" s="16">
         <v>0</v>
       </c>
-      <c r="K4" s="9" t="n">
+      <c r="K4" s="16">
         <v>0</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="O4" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="Q4" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="R4" s="8" t="s">
+      <c r="R4" s="15" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:18" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="I5" s="9" t="n">
+      <c r="I5" s="16">
         <v>27</v>
       </c>
-      <c r="J5" s="9" t="n">
+      <c r="J5" s="16">
         <v>22</v>
       </c>
-      <c r="K5" s="9" t="n">
-        <v>0.8148</v>
-      </c>
-      <c r="L5" s="6" t="s">
+      <c r="K5" s="16">
+        <v>0.81479999999999997</v>
+      </c>
+      <c r="L5" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="O5" s="8" t="s">
+      <c r="O5" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="P5" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="Q5" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="R5" s="8" t="s">
+      <c r="R5" s="15" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:18" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="I6" s="9" t="n">
+      <c r="I6" s="16">
         <v>27</v>
       </c>
-      <c r="J6" s="9" t="n">
+      <c r="J6" s="16">
         <v>22</v>
       </c>
-      <c r="K6" s="9" t="n">
-        <v>0.8148</v>
-      </c>
-      <c r="L6" s="6" t="s">
+      <c r="K6" s="16">
+        <v>0.81479999999999997</v>
+      </c>
+      <c r="L6" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="M6" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="N6" s="6" t="s">
+      <c r="N6" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="O6" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="P6" s="6" t="s">
+      <c r="P6" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="Q6" s="6" t="s">
+      <c r="Q6" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="R6" s="8" t="s">
+      <c r="R6" s="15" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:18" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="I7" s="16">
         <v>27</v>
       </c>
-      <c r="J7" s="9" t="n">
+      <c r="J7" s="16">
         <v>22</v>
       </c>
-      <c r="K7" s="9" t="n">
-        <v>0.8148</v>
-      </c>
-      <c r="L7" s="6" t="s">
+      <c r="K7" s="16">
+        <v>0.81479999999999997</v>
+      </c>
+      <c r="L7" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="M7" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="N7" s="6" t="s">
+      <c r="N7" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="O7" s="8" t="s">
+      <c r="O7" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="P7" s="6" t="s">
+      <c r="P7" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="Q7" s="6" t="s">
+      <c r="Q7" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="R7" s="8" t="s">
+      <c r="R7" s="15" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+    <row r="8" spans="1:18" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="I8" s="9" t="n">
+      <c r="I8" s="16">
         <v>20</v>
       </c>
-      <c r="J8" s="9" t="n">
+      <c r="J8" s="16">
         <v>11</v>
       </c>
-      <c r="K8" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="L8" s="6" t="s">
+      <c r="K8" s="16">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L8" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="M8" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="N8" s="6" t="s">
+      <c r="N8" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="O8" s="8" t="s">
+      <c r="O8" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="P8" s="6" t="s">
+      <c r="P8" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="Q8" s="6" t="s">
+      <c r="Q8" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="R8" s="8" t="s">
+      <c r="R8" s="15" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+    <row r="9" spans="1:18" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="I9" s="9" t="n">
+      <c r="I9" s="16">
         <v>20</v>
       </c>
-      <c r="J9" s="9" t="n">
+      <c r="J9" s="16">
         <v>11</v>
       </c>
-      <c r="K9" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="L9" s="6" t="s">
+      <c r="K9" s="16">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L9" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="M9" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="N9" s="6" t="s">
+      <c r="N9" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="O9" s="8" t="s">
+      <c r="O9" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="P9" s="6" t="s">
+      <c r="P9" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="Q9" s="6" t="s">
+      <c r="Q9" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="R9" s="8" t="s">
+      <c r="R9" s="15" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:18" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="I10" s="9" t="n">
+      <c r="I10" s="16">
         <v>20</v>
       </c>
-      <c r="J10" s="9" t="n">
+      <c r="J10" s="16">
         <v>11</v>
       </c>
-      <c r="K10" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="L10" s="6" t="s">
+      <c r="K10" s="16">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="L10" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="M10" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="N10" s="6" t="s">
+      <c r="N10" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="O10" s="8" t="s">
+      <c r="O10" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="P10" s="6" t="s">
+      <c r="P10" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="Q10" s="6" t="s">
+      <c r="Q10" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="R10" s="8" t="s">
+      <c r="R10" s="15" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:18" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="I11" s="16">
         <v>10</v>
       </c>
-      <c r="J11" s="9" t="n">
+      <c r="J11" s="16">
         <v>8</v>
       </c>
-      <c r="K11" s="9" t="n">
+      <c r="K11" s="16">
         <v>0.8</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="L11" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="M11" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="N11" s="6" t="s">
+      <c r="N11" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="O11" s="8" t="s">
+      <c r="O11" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="P11" s="6" t="s">
+      <c r="P11" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="Q11" s="6" t="s">
+      <c r="Q11" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="R11" s="8" t="s">
+      <c r="R11" s="15" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:18" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="9" t="n">
+      <c r="I12" s="16">
         <v>10</v>
       </c>
-      <c r="J12" s="9" t="n">
+      <c r="J12" s="16">
         <v>8</v>
       </c>
-      <c r="K12" s="9" t="n">
+      <c r="K12" s="16">
         <v>0.8</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="L12" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="M12" s="6" t="s">
+      <c r="M12" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="N12" s="6" t="s">
+      <c r="N12" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="O12" s="8" t="s">
+      <c r="O12" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="P12" s="6" t="s">
+      <c r="P12" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="Q12" s="6" t="s">
+      <c r="Q12" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="R12" s="8" t="s">
+      <c r="R12" s="15" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+    <row r="13" spans="1:18" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="I13" s="9" t="n">
+      <c r="I13" s="16">
         <v>10</v>
       </c>
-      <c r="J13" s="9" t="n">
+      <c r="J13" s="16">
         <v>8</v>
       </c>
-      <c r="K13" s="9" t="n">
+      <c r="K13" s="16">
         <v>0.8</v>
       </c>
-      <c r="L13" s="6" t="s">
+      <c r="L13" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="M13" s="6" t="s">
+      <c r="M13" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="N13" s="6" t="s">
+      <c r="N13" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="O13" s="8" t="s">
+      <c r="O13" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="P13" s="6" t="s">
+      <c r="P13" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="Q13" s="6" t="s">
+      <c r="Q13" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="R13" s="8" t="s">
+      <c r="R13" s="15" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:18" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="I14" s="9" t="n">
+      <c r="I14" s="16">
         <v>15</v>
       </c>
-      <c r="J14" s="9" t="n">
+      <c r="J14" s="16">
         <v>7</v>
       </c>
-      <c r="K14" s="9" t="n">
+      <c r="K14" s="16">
         <v>0.4667</v>
       </c>
-      <c r="L14" s="6" t="s">
+      <c r="L14" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="M14" s="6" t="s">
+      <c r="M14" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="N14" s="6" t="s">
+      <c r="N14" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="O14" s="8" t="s">
+      <c r="O14" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="P14" s="6" t="s">
+      <c r="P14" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="Q14" s="6" t="s">
+      <c r="Q14" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="R14" s="8" t="s">
+      <c r="R14" s="15" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:18" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="I15" s="9" t="n">
+      <c r="I15" s="16">
         <v>15</v>
       </c>
-      <c r="J15" s="9" t="n">
+      <c r="J15" s="16">
         <v>7</v>
       </c>
-      <c r="K15" s="9" t="n">
+      <c r="K15" s="16">
         <v>0.4667</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="L15" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="M15" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="N15" s="6" t="s">
+      <c r="N15" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="O15" s="8" t="s">
+      <c r="O15" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="P15" s="6" t="s">
+      <c r="P15" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="Q15" s="6" t="s">
+      <c r="Q15" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="R15" s="8" t="s">
+      <c r="R15" s="15" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+    <row r="16" spans="1:18" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="I16" s="9" t="n">
+      <c r="I16" s="16">
         <v>15</v>
       </c>
-      <c r="J16" s="9" t="n">
+      <c r="J16" s="16">
         <v>7</v>
       </c>
-      <c r="K16" s="9" t="n">
+      <c r="K16" s="16">
         <v>0.4667</v>
       </c>
-      <c r="L16" s="6" t="s">
+      <c r="L16" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="M16" s="6" t="s">
+      <c r="M16" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="N16" s="6" t="s">
+      <c r="N16" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="O16" s="8" t="s">
+      <c r="O16" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="P16" s="6" t="s">
+      <c r="P16" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="Q16" s="6" t="s">
+      <c r="Q16" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="R16" s="8" t="s">
+      <c r="R16" s="15" t="s">
         <v>179</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R16"/>
-  <conditionalFormatting sqref="H2:H16">
-    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
-      <formula>"EXCLUIDO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L16">
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
-      <formula>"si"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
-      <formula>"NO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P16">
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
-      <formula>"SI"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
-      <formula>"NO"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
-      <formula>"PARCIAL"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q16">
-    <cfRule type="cellIs" priority="8" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
-      <formula>"CORRIGE"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
-      <formula>"CONFIRMA"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DF04F8D-F1AE-4FD0-855D-A463ADE65CC7}">
   <dimension ref="A1:L28"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="88"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="7" width="8" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="88" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="1" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="9" t="n">
+      <c r="F2" s="19">
         <v>10</v>
       </c>
-      <c r="G2" s="9" t="n">
+      <c r="G2" s="19">
         <v>7</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="J2" s="9" t="n">
+      <c r="J2" s="19">
         <v>0</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="L2" s="8"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="L2" s="20"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="F3" s="9" t="n">
+      <c r="F3" s="19">
         <v>7</v>
       </c>
-      <c r="G3" s="9" t="n">
+      <c r="G3" s="19">
         <v>0</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="J3" s="9" t="n">
+      <c r="J3" s="19">
         <v>1</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="L3" s="8"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="L3" s="20"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="19">
         <v>9</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="19">
         <v>0</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="J4" s="9" t="n">
+      <c r="J4" s="19">
         <v>1</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="L4" s="8"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="L4" s="20"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="19">
         <v>5</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="J5" s="9" t="n">
+      <c r="J5" s="19">
         <v>0</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="L5" s="8"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="L5" s="20"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="19">
         <v>4</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="J6" s="9" t="n">
+      <c r="J6" s="19">
         <v>1</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="L6" s="8"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="L6" s="20"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="19">
         <v>16</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="19">
         <v>2</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="J7" s="9" t="n">
+      <c r="J7" s="19">
         <v>0</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="L7" s="8"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="L7" s="20"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="19">
         <v>27</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="19">
         <v>6</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="J8" s="9" t="n">
+      <c r="J8" s="19">
         <v>1</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="L8" s="8"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+      <c r="L8" s="20"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="19">
         <v>18</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="19">
         <v>1</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="J9" s="9" t="n">
+      <c r="J9" s="19">
         <v>1</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="L9" s="8"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+      <c r="L9" s="20"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="19">
         <v>25</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="19">
         <v>8</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="J10" s="9" t="n">
+      <c r="J10" s="19">
         <v>1</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="L10" s="8"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+      <c r="L10" s="20"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="19">
         <v>17</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="19">
         <v>7</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="J11" s="9" t="n">
+      <c r="J11" s="19">
         <v>1</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="L11" s="8"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="L11" s="20"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="19">
         <v>25</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="19">
         <v>0</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="J12" s="9" t="n">
+      <c r="J12" s="19">
         <v>1</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="K12" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="L12" s="8"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+      <c r="L12" s="20"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="19">
         <v>25</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G13" s="19">
         <v>0</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="J13" s="9" t="n">
+      <c r="J13" s="19">
         <v>1</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="K13" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="L13" s="8"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+      <c r="L13" s="20"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="19">
         <v>7</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="19">
         <v>2</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I14" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="J14" s="9" t="n">
+      <c r="J14" s="19">
         <v>1</v>
       </c>
-      <c r="K14" s="6" t="s">
+      <c r="K14" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="L14" s="8"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+      <c r="L14" s="20"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="19">
         <v>16</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="19">
         <v>4</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I15" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="J15" s="9" t="n">
+      <c r="J15" s="19">
         <v>0</v>
       </c>
-      <c r="K15" s="6" t="s">
+      <c r="K15" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="L15" s="8"/>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="L15" s="20"/>
+    </row>
+    <row r="16" spans="1:12" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" s="19">
         <v>18</v>
       </c>
-      <c r="G16" s="9" t="n">
+      <c r="G16" s="19">
         <v>2</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="J16" s="9"/>
-      <c r="K16" s="6" t="s">
+      <c r="J16" s="19"/>
+      <c r="K16" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="L16" s="8" t="s">
+      <c r="L16" s="20" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="11" t="s">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="E18" s="12" t="n">
-        <f aca="false">COUNTIF(K2:K16,"si")</f>
+      <c r="E18" s="22">
+        <f>COUNTIF(K2:K16,"si")</f>
         <v>14</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="11" t="s">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B19" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="E19" s="12" t="n">
-        <f aca="false">SUM(J2:J16)</f>
+      <c r="E19" s="22">
+        <f>SUM(J2:J16)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="13" t="s">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B20" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="E20" s="14" t="n">
-        <f aca="false">SUM(J2:J16)/COUNTIF(K2:K16,"si")</f>
-        <v>0.714285714285714</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="11" t="s">
+      <c r="E20" s="24">
+        <f>SUM(J2:J16)/COUNTIF(K2:K16,"si")</f>
+        <v>0.7142857142857143</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="E21" s="12" t="n">
-        <f aca="false">COUNTIFS(E2:E16,"0",K2:K16,"si")</f>
+      <c r="E21" s="22">
+        <f>COUNTIFS(E2:E16,"0",K2:K16,"si")</f>
         <v>6</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="11" t="s">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="E22" s="12" t="n">
-        <f aca="false">COUNTIFS(E2:E16,"P",K2:K16,"si")</f>
+      <c r="E22" s="22">
+        <f>COUNTIFS(E2:E16,"P",K2:K16,"si")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="11" t="s">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="E23" s="12" t="n">
-        <f aca="false">COUNTIFS(E2:E16,"1",K2:K16,"si")</f>
+      <c r="E23" s="22">
+        <f>COUNTIFS(E2:E16,"1",K2:K16,"si")</f>
         <v>6</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="11" t="s">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="E24" s="12" t="n">
-        <f aca="false">COUNTIFS(I2:I16,"0",K2:K16,"si")</f>
+      <c r="E24" s="22">
+        <f>COUNTIFS(I2:I16,"0",K2:K16,"si")</f>
         <v>5</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="11" t="s">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="E25" s="12" t="n">
-        <f aca="false">COUNTIFS(I2:I16,"P",K2:K16,"si")</f>
+      <c r="E25" s="22">
+        <f>COUNTIFS(I2:I16,"P",K2:K16,"si")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="11" t="s">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="E26" s="12" t="n">
-        <f aca="false">COUNTIFS(I2:I16,"1",K2:K16,"si")</f>
+      <c r="E26" s="22">
+        <f>COUNTIFS(I2:I16,"1",K2:K16,"si")</f>
         <v>8</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="13" t="s">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="E27" s="14" t="n">
-        <f aca="false">(E21*E24+E22*E25+E23*E26)/(E18*E18)</f>
-        <v>0.408163265306122</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="13" t="s">
+      <c r="E27" s="24">
+        <f>(E21*E24+E22*E25+E23*E26)/(E18*E18)</f>
+        <v>0.40816326530612246</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28" s="23" t="s">
         <v>201</v>
       </c>
-      <c r="E28" s="14" t="n">
-        <f aca="false">(E20-E27)/(1-E27)</f>
-        <v>0.517241379310345</v>
-      </c>
-      <c r="F28" s="15" t="s">
+      <c r="E28" s="24">
+        <f>(E20-E27)/(1-E27)</f>
+        <v>0.51724137931034486</v>
+      </c>
+      <c r="F28" s="25" t="s">
         <v>202</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L28"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>